--- a/data_dictionary/NYC_Gov_Spending.xlsx
+++ b/data_dictionary/NYC_Gov_Spending.xlsx
@@ -1,19 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11102"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11130"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/enriqueduval/Documents/CIS9440/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/enriqueduval/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A1DE91EB-00E9-8F42-A370-130F3C58A62E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E8E329B-8C2B-4446-A734-CCDCE4B8DE72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1080" yWindow="1260" windowWidth="27640" windowHeight="16740" xr2:uid="{519734E2-91C9-B649-9F88-AE09B8E22DD5}"/>
+    <workbookView xWindow="29560" yWindow="660" windowWidth="38100" windowHeight="20800" activeTab="1" xr2:uid="{519734E2-91C9-B649-9F88-AE09B8E22DD5}"/>
   </bookViews>
   <sheets>
     <sheet name="Data Dictionary" sheetId="1" r:id="rId1"/>
+    <sheet name="Data mapping" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="333" uniqueCount="191">
   <si>
     <t>Field Name</t>
   </si>
@@ -381,12 +382,264 @@
   <si>
     <t>“z81”</t>
   </si>
+  <si>
+    <t>dw_table</t>
+  </si>
+  <si>
+    <t>dw_column</t>
+  </si>
+  <si>
+    <t>business_name</t>
+  </si>
+  <si>
+    <t>data_type</t>
+  </si>
+  <si>
+    <t>grain_or_role</t>
+  </si>
+  <si>
+    <t>source_table</t>
+  </si>
+  <si>
+    <t>source_column</t>
+  </si>
+  <si>
+    <t>transform_logic</t>
+  </si>
+  <si>
+    <t>agency_id</t>
+  </si>
+  <si>
+    <t>Agency Key</t>
+  </si>
+  <si>
+    <t>STRING</t>
+  </si>
+  <si>
+    <t>Surrogate PK</t>
+  </si>
+  <si>
+    <t>spending_clean</t>
+  </si>
+  <si>
+    <t>(composite)</t>
+  </si>
+  <si>
+    <t>farm_fingerprint(agency, department, industry, budget_code)</t>
+  </si>
+  <si>
+    <t>Agency Name</t>
+  </si>
+  <si>
+    <t>Dimension attribute</t>
+  </si>
+  <si>
+    <t>distinct over stg_spending, trimmed</t>
+  </si>
+  <si>
+    <t>Department Name</t>
+  </si>
+  <si>
+    <t>Vendor Industry</t>
+  </si>
+  <si>
+    <t>Budget Code</t>
+  </si>
+  <si>
+    <t>dim_agency</t>
+  </si>
+  <si>
+    <t>vendor_id</t>
+  </si>
+  <si>
+    <t>Vendor Key</t>
+  </si>
+  <si>
+    <t>Vendor / Payee</t>
+  </si>
+  <si>
+    <t>dim_vendor</t>
+  </si>
+  <si>
+    <t>normalized spacing</t>
+  </si>
+  <si>
+    <t>expense_category_id</t>
+  </si>
+  <si>
+    <t>Expense Category K</t>
+  </si>
+  <si>
+    <t>farm_fingerprint(expense_category)</t>
+  </si>
+  <si>
+    <t>Expense Category</t>
+  </si>
+  <si>
+    <t>trimmed</t>
+  </si>
+  <si>
+    <t>dim_expense_category</t>
+  </si>
+  <si>
+    <t>spending_category_id</t>
+  </si>
+  <si>
+    <t>Spending Category K</t>
+  </si>
+  <si>
+    <t>Spending Category</t>
+  </si>
+  <si>
+    <t>dim_spending_category</t>
+  </si>
+  <si>
+    <t>dim_mwbe_category</t>
+  </si>
+  <si>
+    <t>farm_fingerprint(payee_name, emerging business, woman_owned_business)</t>
+  </si>
+  <si>
+    <t>date_id</t>
+  </si>
+  <si>
+    <t>Date Key</t>
+  </si>
+  <si>
+    <t>INT64</t>
+  </si>
+  <si>
+    <t>YYYYMMDD integer from issue_date</t>
+  </si>
+  <si>
+    <t>full_date</t>
+  </si>
+  <si>
+    <t>Check Issue Date</t>
+  </si>
+  <si>
+    <t>CAST(issue_date AS DATE)</t>
+  </si>
+  <si>
+    <t>Fiscal Year</t>
+  </si>
+  <si>
+    <t>Attribute / hierarchy</t>
+  </si>
+  <si>
+    <t>dim_date</t>
+  </si>
+  <si>
+    <t>passed through from source</t>
+  </si>
+  <si>
+    <t>fact_spending_id</t>
+  </si>
+  <si>
+    <t>Spending Fact Key</t>
+  </si>
+  <si>
+    <t>Surrogate PK for each check row</t>
+  </si>
+  <si>
+    <t>composite</t>
+  </si>
+  <si>
+    <t>farm_fingerprint(agency, payee_name, issue_date, document_id, check_amount)</t>
+  </si>
+  <si>
+    <t>FK → dim_agency.agency_id</t>
+  </si>
+  <si>
+    <t>stg_spending</t>
+  </si>
+  <si>
+    <t>(via join)</t>
+  </si>
+  <si>
+    <t>joined on agency, department, industry, budget_code</t>
+  </si>
+  <si>
+    <t>FK → dim_vendor.vendor_id</t>
+  </si>
+  <si>
+    <t>joined on payee_name</t>
+  </si>
+  <si>
+    <t>Expense Category Key</t>
+  </si>
+  <si>
+    <t>FK → dim_expense_category</t>
+  </si>
+  <si>
+    <t>joined on expense_category</t>
+  </si>
+  <si>
+    <t>Spending Category Key</t>
+  </si>
+  <si>
+    <t>FK → dim_spending_category</t>
+  </si>
+  <si>
+    <t>joined on spending_category</t>
+  </si>
+  <si>
+    <t>mwbe_category_id</t>
+  </si>
+  <si>
+    <t>MWBE Category Key</t>
+  </si>
+  <si>
+    <t>FK → dim_mwbe_category</t>
+  </si>
+  <si>
+    <t>joined on mwbe_category</t>
+  </si>
+  <si>
+    <t>FK → dim_date.date_id</t>
+  </si>
+  <si>
+    <t>joined on CAST(issue_date AS DATE) to dim_date.full_date</t>
+  </si>
+  <si>
+    <t>Check / Document ID</t>
+  </si>
+  <si>
+    <t>Degenerate dimension</t>
+  </si>
+  <si>
+    <t>carried through from staging</t>
+  </si>
+  <si>
+    <t>Contract ID</t>
+  </si>
+  <si>
+    <t>Helper attribute (analysis field)</t>
+  </si>
+  <si>
+    <t>carried through</t>
+  </si>
+  <si>
+    <t>Check Amount</t>
+  </si>
+  <si>
+    <t>NUMERIC</t>
+  </si>
+  <si>
+    <t>Fact measure</t>
+  </si>
+  <si>
+    <t>cleaned / cast to numeric; outliers + distribution described in profiling report</t>
+  </si>
+  <si>
+    <t>fact_spending</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -400,6 +653,19 @@
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -423,9 +689,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1164,4 +1432,740 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4280BCFF-2574-A248-A0D9-6D649B0FC29F}">
+  <dimension ref="A1:H28"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="19.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.1640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.1640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="27.1640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="63.33203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>128</v>
+      </c>
+      <c r="B2" t="s">
+        <v>115</v>
+      </c>
+      <c r="C2" t="s">
+        <v>116</v>
+      </c>
+      <c r="D2" t="s">
+        <v>117</v>
+      </c>
+      <c r="E2" t="s">
+        <v>118</v>
+      </c>
+      <c r="F2" t="s">
+        <v>119</v>
+      </c>
+      <c r="G2" t="s">
+        <v>120</v>
+      </c>
+      <c r="H2" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>128</v>
+      </c>
+      <c r="B3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" t="s">
+        <v>122</v>
+      </c>
+      <c r="D3" t="s">
+        <v>117</v>
+      </c>
+      <c r="E3" t="s">
+        <v>123</v>
+      </c>
+      <c r="F3" t="s">
+        <v>119</v>
+      </c>
+      <c r="G3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H3" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>128</v>
+      </c>
+      <c r="B4" t="s">
+        <v>76</v>
+      </c>
+      <c r="C4" t="s">
+        <v>125</v>
+      </c>
+      <c r="D4" t="s">
+        <v>117</v>
+      </c>
+      <c r="E4" t="s">
+        <v>123</v>
+      </c>
+      <c r="F4" t="s">
+        <v>119</v>
+      </c>
+      <c r="G4" t="s">
+        <v>76</v>
+      </c>
+      <c r="H4" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>128</v>
+      </c>
+      <c r="B5" t="s">
+        <v>85</v>
+      </c>
+      <c r="C5" t="s">
+        <v>126</v>
+      </c>
+      <c r="D5" t="s">
+        <v>117</v>
+      </c>
+      <c r="E5" t="s">
+        <v>123</v>
+      </c>
+      <c r="F5" t="s">
+        <v>119</v>
+      </c>
+      <c r="G5" t="s">
+        <v>85</v>
+      </c>
+      <c r="H5" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>128</v>
+      </c>
+      <c r="B6" t="s">
+        <v>90</v>
+      </c>
+      <c r="C6" t="s">
+        <v>127</v>
+      </c>
+      <c r="D6" t="s">
+        <v>117</v>
+      </c>
+      <c r="E6" t="s">
+        <v>123</v>
+      </c>
+      <c r="F6" t="s">
+        <v>119</v>
+      </c>
+      <c r="G6" t="s">
+        <v>90</v>
+      </c>
+      <c r="H6" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>132</v>
+      </c>
+      <c r="B7" t="s">
+        <v>129</v>
+      </c>
+      <c r="C7" t="s">
+        <v>130</v>
+      </c>
+      <c r="D7" t="s">
+        <v>117</v>
+      </c>
+      <c r="E7" t="s">
+        <v>118</v>
+      </c>
+      <c r="F7" t="s">
+        <v>119</v>
+      </c>
+      <c r="G7" t="s">
+        <v>24</v>
+      </c>
+      <c r="H7" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>132</v>
+      </c>
+      <c r="B8" t="s">
+        <v>24</v>
+      </c>
+      <c r="C8" t="s">
+        <v>131</v>
+      </c>
+      <c r="D8" t="s">
+        <v>117</v>
+      </c>
+      <c r="E8" t="s">
+        <v>123</v>
+      </c>
+      <c r="F8" t="s">
+        <v>119</v>
+      </c>
+      <c r="G8" t="s">
+        <v>24</v>
+      </c>
+      <c r="H8" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>139</v>
+      </c>
+      <c r="B9" t="s">
+        <v>134</v>
+      </c>
+      <c r="C9" t="s">
+        <v>135</v>
+      </c>
+      <c r="D9" t="s">
+        <v>117</v>
+      </c>
+      <c r="E9" t="s">
+        <v>118</v>
+      </c>
+      <c r="F9" t="s">
+        <v>119</v>
+      </c>
+      <c r="G9" t="s">
+        <v>44</v>
+      </c>
+      <c r="H9" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>139</v>
+      </c>
+      <c r="B10" t="s">
+        <v>44</v>
+      </c>
+      <c r="C10" t="s">
+        <v>137</v>
+      </c>
+      <c r="D10" t="s">
+        <v>117</v>
+      </c>
+      <c r="E10" t="s">
+        <v>123</v>
+      </c>
+      <c r="F10" t="s">
+        <v>119</v>
+      </c>
+      <c r="G10" t="s">
+        <v>44</v>
+      </c>
+      <c r="H10" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>143</v>
+      </c>
+      <c r="B11" t="s">
+        <v>140</v>
+      </c>
+      <c r="C11" t="s">
+        <v>141</v>
+      </c>
+      <c r="D11" t="s">
+        <v>117</v>
+      </c>
+      <c r="E11" t="s">
+        <v>118</v>
+      </c>
+      <c r="F11" t="s">
+        <v>119</v>
+      </c>
+      <c r="G11" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>143</v>
+      </c>
+      <c r="B12" t="s">
+        <v>53</v>
+      </c>
+      <c r="C12" t="s">
+        <v>142</v>
+      </c>
+      <c r="D12" t="s">
+        <v>117</v>
+      </c>
+      <c r="E12" t="s">
+        <v>123</v>
+      </c>
+      <c r="F12" t="s">
+        <v>119</v>
+      </c>
+      <c r="G12" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>144</v>
+      </c>
+      <c r="B13" t="s">
+        <v>140</v>
+      </c>
+      <c r="C13" t="s">
+        <v>141</v>
+      </c>
+      <c r="D13" t="s">
+        <v>117</v>
+      </c>
+      <c r="E13" t="s">
+        <v>118</v>
+      </c>
+      <c r="F13" t="s">
+        <v>119</v>
+      </c>
+      <c r="G13" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>144</v>
+      </c>
+      <c r="B14" t="s">
+        <v>53</v>
+      </c>
+      <c r="C14" t="s">
+        <v>142</v>
+      </c>
+      <c r="D14" t="s">
+        <v>117</v>
+      </c>
+      <c r="E14" t="s">
+        <v>123</v>
+      </c>
+      <c r="F14" t="s">
+        <v>119</v>
+      </c>
+      <c r="G14" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>155</v>
+      </c>
+      <c r="B15" t="s">
+        <v>146</v>
+      </c>
+      <c r="C15" t="s">
+        <v>147</v>
+      </c>
+      <c r="D15" t="s">
+        <v>148</v>
+      </c>
+      <c r="E15" t="s">
+        <v>118</v>
+      </c>
+      <c r="F15" t="s">
+        <v>119</v>
+      </c>
+      <c r="G15" t="s">
+        <v>19</v>
+      </c>
+      <c r="H15" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>155</v>
+      </c>
+      <c r="B16" t="s">
+        <v>150</v>
+      </c>
+      <c r="C16" t="s">
+        <v>151</v>
+      </c>
+      <c r="D16" t="s">
+        <v>21</v>
+      </c>
+      <c r="E16" t="s">
+        <v>123</v>
+      </c>
+      <c r="F16" t="s">
+        <v>119</v>
+      </c>
+      <c r="G16" t="s">
+        <v>19</v>
+      </c>
+      <c r="H16" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
+        <v>155</v>
+      </c>
+      <c r="B17" t="s">
+        <v>15</v>
+      </c>
+      <c r="C17" t="s">
+        <v>153</v>
+      </c>
+      <c r="D17" t="s">
+        <v>148</v>
+      </c>
+      <c r="E17" t="s">
+        <v>154</v>
+      </c>
+      <c r="F17" t="s">
+        <v>119</v>
+      </c>
+      <c r="G17" t="s">
+        <v>15</v>
+      </c>
+      <c r="H17" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
+        <v>190</v>
+      </c>
+      <c r="B18" t="s">
+        <v>157</v>
+      </c>
+      <c r="C18" t="s">
+        <v>158</v>
+      </c>
+      <c r="D18" t="s">
+        <v>117</v>
+      </c>
+      <c r="E18" t="s">
+        <v>159</v>
+      </c>
+      <c r="F18" t="s">
+        <v>119</v>
+      </c>
+      <c r="G18" t="s">
+        <v>160</v>
+      </c>
+      <c r="H18" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
+        <v>190</v>
+      </c>
+      <c r="B19" t="s">
+        <v>115</v>
+      </c>
+      <c r="C19" t="s">
+        <v>116</v>
+      </c>
+      <c r="D19" t="s">
+        <v>117</v>
+      </c>
+      <c r="E19" t="s">
+        <v>162</v>
+      </c>
+      <c r="F19" t="s">
+        <v>163</v>
+      </c>
+      <c r="G19" t="s">
+        <v>164</v>
+      </c>
+      <c r="H19" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
+        <v>190</v>
+      </c>
+      <c r="B20" t="s">
+        <v>129</v>
+      </c>
+      <c r="C20" t="s">
+        <v>130</v>
+      </c>
+      <c r="D20" t="s">
+        <v>117</v>
+      </c>
+      <c r="E20" t="s">
+        <v>166</v>
+      </c>
+      <c r="F20" t="s">
+        <v>163</v>
+      </c>
+      <c r="G20" t="s">
+        <v>164</v>
+      </c>
+      <c r="H20" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
+        <v>190</v>
+      </c>
+      <c r="B21" t="s">
+        <v>134</v>
+      </c>
+      <c r="C21" t="s">
+        <v>168</v>
+      </c>
+      <c r="D21" t="s">
+        <v>117</v>
+      </c>
+      <c r="E21" t="s">
+        <v>169</v>
+      </c>
+      <c r="F21" t="s">
+        <v>163</v>
+      </c>
+      <c r="G21" t="s">
+        <v>164</v>
+      </c>
+      <c r="H21" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A22" t="s">
+        <v>190</v>
+      </c>
+      <c r="B22" t="s">
+        <v>140</v>
+      </c>
+      <c r="C22" t="s">
+        <v>171</v>
+      </c>
+      <c r="D22" t="s">
+        <v>117</v>
+      </c>
+      <c r="E22" t="s">
+        <v>172</v>
+      </c>
+      <c r="F22" t="s">
+        <v>163</v>
+      </c>
+      <c r="G22" t="s">
+        <v>164</v>
+      </c>
+      <c r="H22" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A23" t="s">
+        <v>190</v>
+      </c>
+      <c r="B23" t="s">
+        <v>174</v>
+      </c>
+      <c r="C23" t="s">
+        <v>175</v>
+      </c>
+      <c r="D23" t="s">
+        <v>117</v>
+      </c>
+      <c r="E23" t="s">
+        <v>176</v>
+      </c>
+      <c r="F23" t="s">
+        <v>163</v>
+      </c>
+      <c r="G23" t="s">
+        <v>164</v>
+      </c>
+      <c r="H23" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A24" t="s">
+        <v>190</v>
+      </c>
+      <c r="B24" t="s">
+        <v>146</v>
+      </c>
+      <c r="C24" t="s">
+        <v>147</v>
+      </c>
+      <c r="D24" t="s">
+        <v>148</v>
+      </c>
+      <c r="E24" t="s">
+        <v>178</v>
+      </c>
+      <c r="F24" t="s">
+        <v>163</v>
+      </c>
+      <c r="G24" t="s">
+        <v>19</v>
+      </c>
+      <c r="H24" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A25" t="s">
+        <v>190</v>
+      </c>
+      <c r="B25" t="s">
+        <v>34</v>
+      </c>
+      <c r="C25" t="s">
+        <v>180</v>
+      </c>
+      <c r="D25" t="s">
+        <v>117</v>
+      </c>
+      <c r="E25" t="s">
+        <v>181</v>
+      </c>
+      <c r="F25" t="s">
+        <v>119</v>
+      </c>
+      <c r="G25" t="s">
+        <v>34</v>
+      </c>
+      <c r="H25" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A26" t="s">
+        <v>190</v>
+      </c>
+      <c r="B26" t="s">
+        <v>39</v>
+      </c>
+      <c r="C26" t="s">
+        <v>183</v>
+      </c>
+      <c r="D26" t="s">
+        <v>117</v>
+      </c>
+      <c r="E26" t="s">
+        <v>181</v>
+      </c>
+      <c r="F26" t="s">
+        <v>119</v>
+      </c>
+      <c r="G26" t="s">
+        <v>39</v>
+      </c>
+      <c r="H26" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A27" t="s">
+        <v>190</v>
+      </c>
+      <c r="B27" t="s">
+        <v>15</v>
+      </c>
+      <c r="C27" t="s">
+        <v>153</v>
+      </c>
+      <c r="D27" t="s">
+        <v>148</v>
+      </c>
+      <c r="E27" t="s">
+        <v>184</v>
+      </c>
+      <c r="F27" t="s">
+        <v>119</v>
+      </c>
+      <c r="G27" t="s">
+        <v>15</v>
+      </c>
+      <c r="H27" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A28" t="s">
+        <v>190</v>
+      </c>
+      <c r="B28" t="s">
+        <v>57</v>
+      </c>
+      <c r="C28" t="s">
+        <v>186</v>
+      </c>
+      <c r="D28" t="s">
+        <v>187</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="F28" t="s">
+        <v>119</v>
+      </c>
+      <c r="G28" t="s">
+        <v>57</v>
+      </c>
+      <c r="H28" t="s">
+        <v>189</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>